--- a/ranking-old-25-26.xlsx
+++ b/ranking-old-25-26.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AA-DADES\Arxius-Python\Pruebo-streamilt-julio-25\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AA-DADES\Arxius-Python\Liga 25-26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F632DBC5-3C12-4F66-B7FC-F29F8B24F2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_E3A880D482AB3BAFD24633DB95F2A492A0DE138E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35310" yWindow="1980" windowWidth="21600" windowHeight="12975" firstSheet="24" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="0" windowWidth="29040" windowHeight="15720" firstSheet="18" activeTab="38" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="r0" sheetId="1" r:id="rId1"/>
@@ -51,13 +51,14 @@
     <sheet name="r35" sheetId="36" r:id="rId36"/>
     <sheet name="r36" sheetId="37" r:id="rId37"/>
     <sheet name="r37" sheetId="38" r:id="rId38"/>
+    <sheet name="r38" sheetId="39" r:id="rId39"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="20">
   <si>
     <t>Barcelona</t>
   </si>
@@ -3758,9 +3759,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14.33203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -3871,9 +3869,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="16.21875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -3973,6 +3968,116 @@
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
+  <dimension ref="A1:A20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
